--- a/product-definitions/spreadsheet/mean-co2-h2o.xlsx
+++ b/product-definitions/spreadsheet/mean-co2-h2o.xlsx
@@ -251,7 +251,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -277,14 +277,9 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color theme="1"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -308,7 +303,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -329,14 +324,13 @@
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -351,13 +345,13 @@
     <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -369,11 +363,8 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1749,7 +1740,7 @@
       <c r="B3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1789,7 +1780,7 @@
       <c r="B8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="8">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -1797,7 +1788,7 @@
       <c r="B9" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1805,7 +1796,7 @@
       <c r="B10" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1835,7 +1826,7 @@
       <c r="B15" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1867,7 +1858,7 @@
       <c r="B19" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="7" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1875,7 +1866,7 @@
       <c r="B20" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="9">
+      <c r="C20" s="8">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -1883,7 +1874,7 @@
       <c r="B21" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1891,7 +1882,7 @@
       <c r="B22" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1921,7 +1912,7 @@
       <c r="B27" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="7" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1953,7 +1944,7 @@
       <c r="B31" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="7" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1961,7 +1952,7 @@
       <c r="B32" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C32" s="9">
+      <c r="C32" s="8">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -1969,7 +1960,7 @@
       <c r="B33" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="C33" s="9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1977,7 +1968,7 @@
       <c r="B34" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="C34" s="9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2007,7 +1998,7 @@
       <c r="B39" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C39" s="7" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2039,7 +2030,7 @@
       <c r="B43" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C43" s="8" t="s">
+      <c r="C43" s="7" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2047,7 +2038,7 @@
       <c r="B44" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C44" s="9">
+      <c r="C44" s="8">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -2055,7 +2046,7 @@
       <c r="B45" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C45" s="10" t="s">
+      <c r="C45" s="9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2063,7 +2054,7 @@
       <c r="B46" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C46" s="10" t="s">
+      <c r="C46" s="9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2090,90 +2081,90 @@
       </c>
     </row>
     <row r="51" ht="12.0" customHeight="1">
-      <c r="B51" s="11" t="s">
+      <c r="B51" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C51" s="12" t="s">
+      <c r="C51" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="52" ht="12.0" customHeight="1">
-      <c r="B52" s="11" t="s">
+      <c r="B52" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C52" s="13" t="s">
+      <c r="C52" s="12" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="53" ht="12.0" customHeight="1">
-      <c r="B53" s="12" t="s">
+      <c r="B53" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C53" s="14" t="s">
+      <c r="C53" s="13" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="54" ht="12.0" customHeight="1">
-      <c r="B54" s="11" t="s">
+      <c r="B54" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C54" s="15" t="s">
+      <c r="C54" s="14" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="55" ht="12.0" customHeight="1">
-      <c r="B55" s="11" t="s">
+      <c r="B55" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C55" s="16" t="s">
+      <c r="C55" s="15" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="56" ht="12.0" customHeight="1">
-      <c r="B56" s="11" t="s">
+      <c r="B56" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C56" s="17">
+      <c r="C56" s="16">
         <v>-1.0E20</v>
       </c>
     </row>
     <row r="57" ht="12.0" customHeight="1">
-      <c r="B57" s="11" t="s">
+      <c r="B57" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C57" s="10" t="s">
+      <c r="C57" s="9" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="58" ht="12.0" customHeight="1">
-      <c r="B58" s="11" t="s">
+      <c r="B58" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C58" s="10" t="s">
+      <c r="C58" s="9" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="59" ht="12.0" customHeight="1">
-      <c r="B59" s="12" t="s">
+      <c r="B59" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C59" s="18" t="s">
+      <c r="C59" s="17" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="60" ht="12.0" customHeight="1">
-      <c r="B60" s="11" t="s">
+      <c r="B60" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C60" s="12" t="s">
+      <c r="C60" s="11" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="61" ht="12.0" customHeight="1">
-      <c r="B61" s="19" t="s">
+      <c r="B61" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="C61" s="12" t="s">
+      <c r="C61" s="11" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2187,7 +2178,7 @@
       <c r="B64" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C64" s="8" t="s">
+      <c r="C64" s="7" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2219,7 +2210,7 @@
       <c r="B68" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C68" s="8" t="s">
+      <c r="C68" s="7" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2227,7 +2218,7 @@
       <c r="B69" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C69" s="9">
+      <c r="C69" s="8">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -2235,7 +2226,7 @@
       <c r="B70" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C70" s="10" t="s">
+      <c r="C70" s="9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2243,7 +2234,7 @@
       <c r="B71" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C71" s="10" t="s">
+      <c r="C71" s="9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2264,10 +2255,10 @@
       </c>
     </row>
     <row r="74" ht="12.0" customHeight="1">
-      <c r="B74" s="19" t="s">
+      <c r="B74" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="C74" s="12" t="s">
+      <c r="C74" s="11" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2281,7 +2272,7 @@
       <c r="B77" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C77" s="8" t="s">
+      <c r="C77" s="7" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2313,7 +2304,7 @@
       <c r="B81" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C81" s="8" t="s">
+      <c r="C81" s="7" t="s">
         <v>42</v>
       </c>
     </row>
@@ -2321,7 +2312,7 @@
       <c r="B82" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C82" s="9">
+      <c r="C82" s="8">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -2329,7 +2320,7 @@
       <c r="B83" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C83" s="10" t="s">
+      <c r="C83" s="9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2337,7 +2328,7 @@
       <c r="B84" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C84" s="10" t="s">
+      <c r="C84" s="9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2358,10 +2349,10 @@
       </c>
     </row>
     <row r="87" ht="12.0" customHeight="1">
-      <c r="B87" s="19" t="s">
+      <c r="B87" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="C87" s="12" t="s">
+      <c r="C87" s="11" t="s">
         <v>43</v>
       </c>
     </row>
@@ -2375,7 +2366,7 @@
       <c r="B90" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C90" s="8" t="s">
+      <c r="C90" s="7" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2407,7 +2398,7 @@
       <c r="B94" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C94" s="8" t="s">
+      <c r="C94" s="7" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2415,7 +2406,7 @@
       <c r="B95" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C95" s="9">
+      <c r="C95" s="8">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -2423,7 +2414,7 @@
       <c r="B96" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C96" s="10" t="s">
+      <c r="C96" s="9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2431,7 +2422,7 @@
       <c r="B97" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C97" s="10" t="s">
+      <c r="C97" s="9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2452,10 +2443,10 @@
       </c>
     </row>
     <row r="100" ht="12.0" customHeight="1">
-      <c r="B100" s="19" t="s">
+      <c r="B100" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="C100" s="12" t="s">
+      <c r="C100" s="11" t="s">
         <v>43</v>
       </c>
     </row>
@@ -2469,7 +2460,7 @@
       <c r="B103" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C103" s="8" t="s">
+      <c r="C103" s="7" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2501,7 +2492,7 @@
       <c r="B107" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C107" s="8" t="s">
+      <c r="C107" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2509,7 +2500,7 @@
       <c r="B108" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C108" s="9">
+      <c r="C108" s="8">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -2517,7 +2508,7 @@
       <c r="B109" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C109" s="10" t="s">
+      <c r="C109" s="9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2525,7 +2516,7 @@
       <c r="B110" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C110" s="10" t="s">
+      <c r="C110" s="9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2555,7 +2546,7 @@
       <c r="B115" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C115" s="8" t="s">
+      <c r="C115" s="7" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2587,7 +2578,7 @@
       <c r="B119" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C119" s="8" t="s">
+      <c r="C119" s="7" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2595,7 +2586,7 @@
       <c r="B120" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C120" s="9">
+      <c r="C120" s="8">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -2603,7 +2594,7 @@
       <c r="B121" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C121" s="10" t="s">
+      <c r="C121" s="9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2611,7 +2602,7 @@
       <c r="B122" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C122" s="10" t="s">
+      <c r="C122" s="9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2641,7 +2632,7 @@
       <c r="B127" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C127" s="8" t="s">
+      <c r="C127" s="7" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2657,7 +2648,7 @@
       <c r="B129" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C129" s="20">
+      <c r="C129" s="19">
         <v>1.0</v>
       </c>
     </row>
@@ -2673,7 +2664,7 @@
       <c r="B131" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C131" s="8" t="s">
+      <c r="C131" s="7" t="s">
         <v>53</v>
       </c>
     </row>
@@ -2681,7 +2672,7 @@
       <c r="B132" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C132" s="9">
+      <c r="C132" s="8">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -2689,7 +2680,7 @@
       <c r="B133" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C133" s="10" t="s">
+      <c r="C133" s="9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2697,7 +2688,7 @@
       <c r="B134" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C134" s="10" t="s">
+      <c r="C134" s="9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2719,7 +2710,7 @@
     </row>
     <row r="137" ht="12.0" customHeight="1"/>
     <row r="138" ht="12.0" customHeight="1">
-      <c r="A138" s="8" t="s">
+      <c r="A138" s="7" t="s">
         <v>54</v>
       </c>
     </row>
@@ -2727,7 +2718,7 @@
       <c r="B139" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C139" s="8" t="s">
+      <c r="C139" s="7" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2743,7 +2734,7 @@
       <c r="B141" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C141" s="21">
+      <c r="C141" s="20">
         <v>1.0</v>
       </c>
     </row>
@@ -2751,7 +2742,7 @@
       <c r="B142" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D142" s="8" t="s">
+      <c r="D142" s="7" t="s">
         <v>54</v>
       </c>
     </row>
@@ -2759,7 +2750,7 @@
       <c r="B143" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C143" s="8" t="s">
+      <c r="C143" s="7" t="s">
         <v>55</v>
       </c>
     </row>
@@ -2767,7 +2758,7 @@
       <c r="B144" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C144" s="9">
+      <c r="C144" s="8">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -2775,7 +2766,7 @@
       <c r="B145" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C145" s="10" t="s">
+      <c r="C145" s="9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2783,7 +2774,7 @@
       <c r="B146" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C146" s="10" t="s">
+      <c r="C146" s="9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2813,7 +2804,7 @@
       <c r="B151" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C151" s="8" t="s">
+      <c r="C151" s="7" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2829,7 +2820,7 @@
       <c r="B153" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C153" s="20">
+      <c r="C153" s="19">
         <v>1.0</v>
       </c>
     </row>
@@ -2837,7 +2828,7 @@
       <c r="B154" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C154" s="20"/>
+      <c r="C154" s="19"/>
     </row>
     <row r="155" ht="12.0" customHeight="1">
       <c r="B155" s="7" t="s">
@@ -2848,18 +2839,18 @@
       </c>
     </row>
     <row r="156" ht="12.0" customHeight="1">
-      <c r="B156" s="11" t="s">
+      <c r="B156" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="C156" s="12" t="s">
+      <c r="C156" s="11" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="157">
-      <c r="B157" s="18" t="s">
+    <row r="157" ht="15.75" customHeight="1">
+      <c r="B157" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="C157" s="22" t="s">
+      <c r="C157" s="21" t="s">
         <v>62</v>
       </c>
     </row>
@@ -2873,7 +2864,7 @@
       <c r="B160" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C160" s="8" t="s">
+      <c r="C160" s="7" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2889,7 +2880,7 @@
       <c r="B162" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C162" s="20">
+      <c r="C162" s="19">
         <v>1.0</v>
       </c>
     </row>
@@ -2897,7 +2888,7 @@
       <c r="B163" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C163" s="20"/>
+      <c r="C163" s="19"/>
     </row>
     <row r="164" ht="12.0" customHeight="1">
       <c r="B164" s="7" t="s">
@@ -2908,18 +2899,18 @@
       </c>
     </row>
     <row r="165" ht="12.0" customHeight="1">
-      <c r="B165" s="11" t="s">
+      <c r="B165" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="C165" s="12" t="s">
+      <c r="C165" s="11" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="166">
-      <c r="B166" s="18" t="s">
+    <row r="166" ht="15.75" customHeight="1">
+      <c r="B166" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="C166" s="22" t="s">
+      <c r="C166" s="21" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2933,7 +2924,7 @@
       <c r="B169" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C169" s="8" t="s">
+      <c r="C169" s="7" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2949,7 +2940,7 @@
       <c r="B171" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C171" s="20">
+      <c r="C171" s="19">
         <v>1.0</v>
       </c>
     </row>
@@ -2957,29 +2948,29 @@
       <c r="B172" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C172" s="20"/>
+      <c r="C172" s="19"/>
     </row>
     <row r="173" ht="12.0" customHeight="1">
       <c r="B173" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C173" s="8" t="s">
+      <c r="C173" s="7" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="174" ht="12.0" customHeight="1">
-      <c r="B174" s="11" t="s">
+      <c r="B174" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="C174" s="12" t="s">
+      <c r="C174" s="11" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="175">
-      <c r="B175" s="18" t="s">
+    <row r="175" ht="15.75" customHeight="1">
+      <c r="B175" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="C175" s="23" t="s">
+      <c r="C175" s="21" t="s">
         <v>69</v>
       </c>
     </row>
@@ -2993,7 +2984,7 @@
       <c r="B178" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C178" s="8" t="s">
+      <c r="C178" s="7" t="s">
         <v>57</v>
       </c>
     </row>
@@ -3009,7 +3000,7 @@
       <c r="B180" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C180" s="20">
+      <c r="C180" s="19">
         <v>1.0</v>
       </c>
     </row>
@@ -3017,29 +3008,29 @@
       <c r="B181" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C181" s="20"/>
+      <c r="C181" s="19"/>
     </row>
     <row r="182" ht="12.0" customHeight="1">
       <c r="B182" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C182" s="8" t="s">
+      <c r="C182" s="7" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="183" ht="12.0" customHeight="1">
-      <c r="B183" s="11" t="s">
+      <c r="B183" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="C183" s="12" t="s">
+      <c r="C183" s="11" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="184">
-      <c r="B184" s="18" t="s">
+    <row r="184" ht="15.75" customHeight="1">
+      <c r="B184" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="C184" s="23" t="s">
+      <c r="C184" s="21" t="s">
         <v>72</v>
       </c>
     </row>
@@ -3059,14 +3050,14 @@
     <row r="198" ht="12.0" customHeight="1"/>
     <row r="199" ht="12.0" customHeight="1"/>
     <row r="200" ht="12.0" customHeight="1">
-      <c r="C200" s="20"/>
+      <c r="C200" s="19"/>
     </row>
     <row r="201" ht="12.0" customHeight="1">
-      <c r="C201" s="20"/>
+      <c r="C201" s="19"/>
     </row>
     <row r="202" ht="12.0" customHeight="1"/>
     <row r="203" ht="12.0" customHeight="1">
-      <c r="C203" s="20"/>
+      <c r="C203" s="19"/>
     </row>
     <row r="204" ht="12.0" customHeight="1"/>
     <row r="205" ht="12.0" customHeight="1"/>
